--- a/dataAcquisition/Motec_MP/channels/channels.xlsx
+++ b/dataAcquisition/Motec_MP/channels/channels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SimEnv\dataAcquisition\Motec_MP\channels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A56161D-6A4A-48C3-9473-C656B52220C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1C7E4C-9398-4992-A9BD-303D0A6570EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3072" yWindow="660" windowWidth="18180" windowHeight="13740" xr2:uid="{6EEC8272-D558-43BF-A2F2-0B52778D7332}"/>
+    <workbookView xWindow="1560" yWindow="420" windowWidth="20136" windowHeight="13680" xr2:uid="{6EEC8272-D558-43BF-A2F2-0B52778D7332}"/>
   </bookViews>
   <sheets>
     <sheet name="channels" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet2" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">channels!$B$1:$B$992</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">channels!$B$1:$B$1014</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3499,6 +3499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA4F88A-3EEB-45AF-91DF-E65A060D6362}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E1014"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3569,7 +3570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -3609,7 +3610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -3633,7 +3634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -3641,7 +3642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -3649,7 +3650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -3657,7 +3658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -3665,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -3681,7 +3682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -3721,7 +3722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -3729,7 +3730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -3737,7 +3738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -3745,7 +3746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -3753,7 +3754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -3785,7 +3786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -3793,7 +3794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -3801,7 +3802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -3809,7 +3810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -3817,7 +3818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -3825,7 +3826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -3841,7 +3842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -3849,7 +3850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -3857,7 +3858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -3865,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -3873,7 +3874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -3881,7 +3882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -3889,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -3897,7 +3898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -3905,7 +3906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -3913,7 +3914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>48</v>
       </c>
@@ -3921,7 +3922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -3929,7 +3930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>50</v>
       </c>
@@ -3937,7 +3938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>51</v>
       </c>
@@ -3945,7 +3946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>52</v>
       </c>
@@ -3953,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>53</v>
       </c>
@@ -3961,7 +3962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>54</v>
       </c>
@@ -3969,7 +3970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>55</v>
       </c>
@@ -3977,7 +3978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>56</v>
       </c>
@@ -3985,7 +3986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -3993,7 +3994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>58</v>
       </c>
@@ -4001,7 +4002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -4009,7 +4010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>60</v>
       </c>
@@ -4017,7 +4018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>61</v>
       </c>
@@ -4025,7 +4026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>62</v>
       </c>
@@ -4033,7 +4034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -4041,7 +4042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>64</v>
       </c>
@@ -4049,7 +4050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>65</v>
       </c>
@@ -4057,7 +4058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>66</v>
       </c>
@@ -4065,7 +4066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>67</v>
       </c>
@@ -4073,7 +4074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>68</v>
       </c>
@@ -4081,7 +4082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -4089,7 +4090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>70</v>
       </c>
@@ -4097,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>71</v>
       </c>
@@ -4105,7 +4106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>72</v>
       </c>
@@ -4113,7 +4114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>73</v>
       </c>
@@ -4121,7 +4122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>74</v>
       </c>
@@ -4137,7 +4138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>76</v>
       </c>
@@ -4145,7 +4146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>77</v>
       </c>
@@ -4153,7 +4154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>78</v>
       </c>
@@ -4161,7 +4162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>79</v>
       </c>
@@ -4169,7 +4170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>80</v>
       </c>
@@ -4177,7 +4178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>81</v>
       </c>
@@ -4185,7 +4186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>82</v>
       </c>
@@ -4193,7 +4194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>83</v>
       </c>
@@ -4201,7 +4202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>84</v>
       </c>
@@ -4209,7 +4210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>85</v>
       </c>
@@ -4217,7 +4218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>86</v>
       </c>
@@ -4225,7 +4226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>87</v>
       </c>
@@ -4233,7 +4234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>88</v>
       </c>
@@ -4241,7 +4242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>89</v>
       </c>
@@ -4249,7 +4250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>90</v>
       </c>
@@ -4257,7 +4258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>91</v>
       </c>
@@ -4265,7 +4266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>92</v>
       </c>
@@ -4273,7 +4274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>93</v>
       </c>
@@ -4281,7 +4282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>94</v>
       </c>
@@ -4289,7 +4290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>95</v>
       </c>
@@ -4297,7 +4298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>96</v>
       </c>
@@ -4305,7 +4306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>97</v>
       </c>
@@ -4313,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>98</v>
       </c>
@@ -4321,7 +4322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>99</v>
       </c>
@@ -4329,7 +4330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>100</v>
       </c>
@@ -4337,7 +4338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>101</v>
       </c>
@@ -4345,7 +4346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>102</v>
       </c>
@@ -4353,7 +4354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -4361,7 +4362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>104</v>
       </c>
@@ -4369,7 +4370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>105</v>
       </c>
@@ -4377,7 +4378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>106</v>
       </c>
@@ -4385,7 +4386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>107</v>
       </c>
@@ -4393,7 +4394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -4401,7 +4402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -4409,7 +4410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>110</v>
       </c>
@@ -4417,7 +4418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>111</v>
       </c>
@@ -4425,7 +4426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>112</v>
       </c>
@@ -4433,7 +4434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>113</v>
       </c>
@@ -4441,7 +4442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>114</v>
       </c>
@@ -4449,7 +4450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>115</v>
       </c>
@@ -4457,7 +4458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>116</v>
       </c>
@@ -4465,7 +4466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>117</v>
       </c>
@@ -4473,7 +4474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>118</v>
       </c>
@@ -4481,7 +4482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>119</v>
       </c>
@@ -4489,7 +4490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>120</v>
       </c>
@@ -4497,7 +4498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>121</v>
       </c>
@@ -4505,7 +4506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>122</v>
       </c>
@@ -4513,7 +4514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>123</v>
       </c>
@@ -4521,7 +4522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>124</v>
       </c>
@@ -4529,7 +4530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>125</v>
       </c>
@@ -4537,7 +4538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>126</v>
       </c>
@@ -4545,7 +4546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>127</v>
       </c>
@@ -4553,7 +4554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>128</v>
       </c>
@@ -4561,7 +4562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>129</v>
       </c>
@@ -4569,7 +4570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>130</v>
       </c>
@@ -4577,7 +4578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>131</v>
       </c>
@@ -4585,7 +4586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>132</v>
       </c>
@@ -4593,7 +4594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>133</v>
       </c>
@@ -4601,7 +4602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>134</v>
       </c>
@@ -4609,7 +4610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>135</v>
       </c>
@@ -4617,7 +4618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>136</v>
       </c>
@@ -4625,7 +4626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>137</v>
       </c>
@@ -4633,7 +4634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>138</v>
       </c>
@@ -4641,7 +4642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>139</v>
       </c>
@@ -4649,7 +4650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>140</v>
       </c>
@@ -4657,7 +4658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>141</v>
       </c>
@@ -4665,7 +4666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>142</v>
       </c>
@@ -4673,7 +4674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>143</v>
       </c>
@@ -4689,7 +4690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>145</v>
       </c>
@@ -4697,7 +4698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>146</v>
       </c>
@@ -4705,7 +4706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>147</v>
       </c>
@@ -4713,7 +4714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>148</v>
       </c>
@@ -4721,7 +4722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>149</v>
       </c>
@@ -4729,7 +4730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>150</v>
       </c>
@@ -4737,7 +4738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>151</v>
       </c>
@@ -4745,7 +4746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>152</v>
       </c>
@@ -4753,7 +4754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>153</v>
       </c>
@@ -4761,7 +4762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>154</v>
       </c>
@@ -4769,7 +4770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>155</v>
       </c>
@@ -4777,7 +4778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>156</v>
       </c>
@@ -4785,7 +4786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>157</v>
       </c>
@@ -4825,7 +4826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>162</v>
       </c>
@@ -4833,7 +4834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>163</v>
       </c>
@@ -4841,7 +4842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>164</v>
       </c>
@@ -4849,7 +4850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>165</v>
       </c>
@@ -4857,7 +4858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>166</v>
       </c>
@@ -4865,7 +4866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>167</v>
       </c>
@@ -4873,7 +4874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>168</v>
       </c>
@@ -4881,7 +4882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>169</v>
       </c>
@@ -4889,7 +4890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>170</v>
       </c>
@@ -4897,7 +4898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>171</v>
       </c>
@@ -4905,7 +4906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>172</v>
       </c>
@@ -4913,7 +4914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>173</v>
       </c>
@@ -4921,7 +4922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>174</v>
       </c>
@@ -4929,7 +4930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>175</v>
       </c>
@@ -4937,7 +4938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>176</v>
       </c>
@@ -4945,7 +4946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>177</v>
       </c>
@@ -4953,7 +4954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>178</v>
       </c>
@@ -4961,7 +4962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>179</v>
       </c>
@@ -4969,7 +4970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>180</v>
       </c>
@@ -4977,7 +4978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>181</v>
       </c>
@@ -4985,7 +4986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>182</v>
       </c>
@@ -4993,7 +4994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>183</v>
       </c>
@@ -5001,7 +5002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>184</v>
       </c>
@@ -5009,7 +5010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>185</v>
       </c>
@@ -5017,7 +5018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>186</v>
       </c>
@@ -5025,7 +5026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>187</v>
       </c>
@@ -5033,7 +5034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>188</v>
       </c>
@@ -5041,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>189</v>
       </c>
@@ -5049,7 +5050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>190</v>
       </c>
@@ -5057,7 +5058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>191</v>
       </c>
@@ -5065,7 +5066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>192</v>
       </c>
@@ -5073,7 +5074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>193</v>
       </c>
@@ -5081,7 +5082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>194</v>
       </c>
@@ -5089,7 +5090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>195</v>
       </c>
@@ -5097,7 +5098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>196</v>
       </c>
@@ -5105,7 +5106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>197</v>
       </c>
@@ -5113,7 +5114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>198</v>
       </c>
@@ -5121,7 +5122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>199</v>
       </c>
@@ -5129,7 +5130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>200</v>
       </c>
@@ -5137,7 +5138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>201</v>
       </c>
@@ -5145,7 +5146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>202</v>
       </c>
@@ -5153,7 +5154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>203</v>
       </c>
@@ -5161,7 +5162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>204</v>
       </c>
@@ -5169,7 +5170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>205</v>
       </c>
@@ -5177,7 +5178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>206</v>
       </c>
@@ -5185,7 +5186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>207</v>
       </c>
@@ -5193,7 +5194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>208</v>
       </c>
@@ -5201,7 +5202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>209</v>
       </c>
@@ -5209,7 +5210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>210</v>
       </c>
@@ -5217,7 +5218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>211</v>
       </c>
@@ -5225,7 +5226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>212</v>
       </c>
@@ -5233,7 +5234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>213</v>
       </c>
@@ -5241,7 +5242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>214</v>
       </c>
@@ -5249,7 +5250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>215</v>
       </c>
@@ -5257,7 +5258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>216</v>
       </c>
@@ -5265,7 +5266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>217</v>
       </c>
@@ -5273,7 +5274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>218</v>
       </c>
@@ -5281,7 +5282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>219</v>
       </c>
@@ -5289,7 +5290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>220</v>
       </c>
@@ -5297,7 +5298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>221</v>
       </c>
@@ -5305,7 +5306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>222</v>
       </c>
@@ -5313,7 +5314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>223</v>
       </c>
@@ -5321,7 +5322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>224</v>
       </c>
@@ -5329,7 +5330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>225</v>
       </c>
@@ -5337,7 +5338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>226</v>
       </c>
@@ -5345,7 +5346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>227</v>
       </c>
@@ -5353,7 +5354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>228</v>
       </c>
@@ -5361,7 +5362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>229</v>
       </c>
@@ -5369,7 +5370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>230</v>
       </c>
@@ -5377,7 +5378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>231</v>
       </c>
@@ -5385,7 +5386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>232</v>
       </c>
@@ -5393,7 +5394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>233</v>
       </c>
@@ -5401,7 +5402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>234</v>
       </c>
@@ -5409,7 +5410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>235</v>
       </c>
@@ -5425,7 +5426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>237</v>
       </c>
@@ -5433,7 +5434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>238</v>
       </c>
@@ -5441,7 +5442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>239</v>
       </c>
@@ -5449,7 +5450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>240</v>
       </c>
@@ -5457,7 +5458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>241</v>
       </c>
@@ -5465,7 +5466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>242</v>
       </c>
@@ -5473,7 +5474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>243</v>
       </c>
@@ -5481,7 +5482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>244</v>
       </c>
@@ -5489,7 +5490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>245</v>
       </c>
@@ -5497,7 +5498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>246</v>
       </c>
@@ -5505,7 +5506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>247</v>
       </c>
@@ -5513,7 +5514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>248</v>
       </c>
@@ -5521,7 +5522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>249</v>
       </c>
@@ -5529,7 +5530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>250</v>
       </c>
@@ -5537,7 +5538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>251</v>
       </c>
@@ -5545,7 +5546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>252</v>
       </c>
@@ -5553,7 +5554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>253</v>
       </c>
@@ -5561,7 +5562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>254</v>
       </c>
@@ -5569,7 +5570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>255</v>
       </c>
@@ -5577,7 +5578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>256</v>
       </c>
@@ -5585,7 +5586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>257</v>
       </c>
@@ -5593,7 +5594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>258</v>
       </c>
@@ -5601,7 +5602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>259</v>
       </c>
@@ -5609,7 +5610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>260</v>
       </c>
@@ -5617,7 +5618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>261</v>
       </c>
@@ -5625,7 +5626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>262</v>
       </c>
@@ -5633,7 +5634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>263</v>
       </c>
@@ -5641,7 +5642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>264</v>
       </c>
@@ -5673,7 +5674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>268</v>
       </c>
@@ -5697,7 +5698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>271</v>
       </c>
@@ -5705,7 +5706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>272</v>
       </c>
@@ -5713,7 +5714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>273</v>
       </c>
@@ -5721,7 +5722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>274</v>
       </c>
@@ -5729,7 +5730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>275</v>
       </c>
@@ -5737,7 +5738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>276</v>
       </c>
@@ -5745,7 +5746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>277</v>
       </c>
@@ -5753,7 +5754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>278</v>
       </c>
@@ -5761,7 +5762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>279</v>
       </c>
@@ -5769,7 +5770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>280</v>
       </c>
@@ -5777,7 +5778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>281</v>
       </c>
@@ -5785,7 +5786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>282</v>
       </c>
@@ -5793,7 +5794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>283</v>
       </c>
@@ -5801,7 +5802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>284</v>
       </c>
@@ -5809,7 +5810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>285</v>
       </c>
@@ -5817,7 +5818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>286</v>
       </c>
@@ -5825,7 +5826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>287</v>
       </c>
@@ -5833,7 +5834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>288</v>
       </c>
@@ -5841,7 +5842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>289</v>
       </c>
@@ -5849,7 +5850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>290</v>
       </c>
@@ -5857,7 +5858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>291</v>
       </c>
@@ -5865,7 +5866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>292</v>
       </c>
@@ -5873,7 +5874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>293</v>
       </c>
@@ -5881,7 +5882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>294</v>
       </c>
@@ -5889,7 +5890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>295</v>
       </c>
@@ -5897,7 +5898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>296</v>
       </c>
@@ -5905,7 +5906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>297</v>
       </c>
@@ -5913,7 +5914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>298</v>
       </c>
@@ -5921,7 +5922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>299</v>
       </c>
@@ -5929,7 +5930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>300</v>
       </c>
@@ -5937,7 +5938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>301</v>
       </c>
@@ -5945,7 +5946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>302</v>
       </c>
@@ -5961,7 +5962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>304</v>
       </c>
@@ -5969,7 +5970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>305</v>
       </c>
@@ -5977,7 +5978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>306</v>
       </c>
@@ -5985,7 +5986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>307</v>
       </c>
@@ -5993,7 +5994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>308</v>
       </c>
@@ -6001,7 +6002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>309</v>
       </c>
@@ -6009,7 +6010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>310</v>
       </c>
@@ -6017,7 +6018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>311</v>
       </c>
@@ -6025,7 +6026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>312</v>
       </c>
@@ -6033,7 +6034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>313</v>
       </c>
@@ -6041,7 +6042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>314</v>
       </c>
@@ -6049,7 +6050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>315</v>
       </c>
@@ -6057,7 +6058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>316</v>
       </c>
@@ -6065,7 +6066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>317</v>
       </c>
@@ -6073,7 +6074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>318</v>
       </c>
@@ -6089,7 +6090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>320</v>
       </c>
@@ -6097,7 +6098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>321</v>
       </c>
@@ -6105,7 +6106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>322</v>
       </c>
@@ -6113,7 +6114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>323</v>
       </c>
@@ -6121,7 +6122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>324</v>
       </c>
@@ -6129,7 +6130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>325</v>
       </c>
@@ -6137,7 +6138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>326</v>
       </c>
@@ -6145,7 +6146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>327</v>
       </c>
@@ -6153,7 +6154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>328</v>
       </c>
@@ -6161,7 +6162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>329</v>
       </c>
@@ -6169,7 +6170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>330</v>
       </c>
@@ -6177,7 +6178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>331</v>
       </c>
@@ -6185,7 +6186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>332</v>
       </c>
@@ -6193,7 +6194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>333</v>
       </c>
@@ -6201,7 +6202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>334</v>
       </c>
@@ -6209,7 +6210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>335</v>
       </c>
@@ -6217,7 +6218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>336</v>
       </c>
@@ -6225,7 +6226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>337</v>
       </c>
@@ -6233,7 +6234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>338</v>
       </c>
@@ -6241,7 +6242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>339</v>
       </c>
@@ -6249,7 +6250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>340</v>
       </c>
@@ -6257,7 +6258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>341</v>
       </c>
@@ -6265,7 +6266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>342</v>
       </c>
@@ -6273,7 +6274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>343</v>
       </c>
@@ -6281,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>344</v>
       </c>
@@ -6289,7 +6290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>345</v>
       </c>
@@ -6297,7 +6298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>346</v>
       </c>
@@ -6305,7 +6306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>347</v>
       </c>
@@ -6313,7 +6314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>348</v>
       </c>
@@ -6321,7 +6322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>349</v>
       </c>
@@ -6329,7 +6330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>350</v>
       </c>
@@ -6337,7 +6338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>351</v>
       </c>
@@ -6345,7 +6346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>352</v>
       </c>
@@ -6353,7 +6354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>353</v>
       </c>
@@ -6361,7 +6362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>354</v>
       </c>
@@ -6369,7 +6370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>355</v>
       </c>
@@ -6377,7 +6378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>356</v>
       </c>
@@ -6385,7 +6386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>357</v>
       </c>
@@ -6393,7 +6394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>358</v>
       </c>
@@ -6401,7 +6402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>359</v>
       </c>
@@ -6409,7 +6410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>360</v>
       </c>
@@ -6417,7 +6418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>361</v>
       </c>
@@ -6425,7 +6426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>362</v>
       </c>
@@ -6433,7 +6434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>363</v>
       </c>
@@ -6441,7 +6442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>364</v>
       </c>
@@ -6449,7 +6450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>365</v>
       </c>
@@ -6457,7 +6458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>366</v>
       </c>
@@ -6465,7 +6466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>367</v>
       </c>
@@ -6473,7 +6474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>368</v>
       </c>
@@ -6481,7 +6482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>369</v>
       </c>
@@ -6489,7 +6490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>370</v>
       </c>
@@ -6497,7 +6498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>371</v>
       </c>
@@ -6505,7 +6506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>372</v>
       </c>
@@ -6513,7 +6514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>373</v>
       </c>
@@ -6521,7 +6522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>374</v>
       </c>
@@ -6529,7 +6530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>375</v>
       </c>
@@ -6537,7 +6538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>376</v>
       </c>
@@ -6545,7 +6546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>377</v>
       </c>
@@ -6553,7 +6554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>378</v>
       </c>
@@ -6561,7 +6562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>379</v>
       </c>
@@ -6569,7 +6570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>380</v>
       </c>
@@ -6577,7 +6578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>381</v>
       </c>
@@ -6585,7 +6586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>382</v>
       </c>
@@ -6593,7 +6594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>383</v>
       </c>
@@ -6601,7 +6602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>384</v>
       </c>
@@ -6609,7 +6610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>385</v>
       </c>
@@ -6617,7 +6618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>386</v>
       </c>
@@ -6625,7 +6626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>387</v>
       </c>
@@ -6633,7 +6634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>388</v>
       </c>
@@ -6641,7 +6642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>389</v>
       </c>
@@ -6649,7 +6650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>390</v>
       </c>
@@ -6665,7 +6666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>392</v>
       </c>
@@ -6673,7 +6674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>393</v>
       </c>
@@ -6681,7 +6682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>394</v>
       </c>
@@ -6689,7 +6690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>395</v>
       </c>
@@ -6697,7 +6698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>396</v>
       </c>
@@ -6777,7 +6778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>406</v>
       </c>
@@ -6785,7 +6786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>407</v>
       </c>
@@ -6793,7 +6794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>408</v>
       </c>
@@ -6801,7 +6802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>409</v>
       </c>
@@ -6809,7 +6810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>410</v>
       </c>
@@ -6817,7 +6818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>411</v>
       </c>
@@ -6857,7 +6858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>416</v>
       </c>
@@ -6865,7 +6866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>417</v>
       </c>
@@ -6873,7 +6874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>418</v>
       </c>
@@ -6881,7 +6882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>419</v>
       </c>
@@ -6889,7 +6890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>420</v>
       </c>
@@ -6897,7 +6898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>421</v>
       </c>
@@ -6905,7 +6906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>422</v>
       </c>
@@ -6913,7 +6914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>423</v>
       </c>
@@ -6921,7 +6922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>424</v>
       </c>
@@ -6929,7 +6930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>425</v>
       </c>
@@ -6937,7 +6938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>426</v>
       </c>
@@ -6945,7 +6946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>427</v>
       </c>
@@ -6995,7 +6996,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>431</v>
       </c>
@@ -7003,7 +7004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>432</v>
       </c>
@@ -7011,7 +7012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>433</v>
       </c>
@@ -7019,7 +7020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>434</v>
       </c>
@@ -7027,7 +7028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>435</v>
       </c>
@@ -7035,7 +7036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>436</v>
       </c>
@@ -7043,7 +7044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>437</v>
       </c>
@@ -7051,7 +7052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>438</v>
       </c>
@@ -7059,7 +7060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>439</v>
       </c>
@@ -7067,7 +7068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>440</v>
       </c>
@@ -7075,7 +7076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>441</v>
       </c>
@@ -7083,7 +7084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>442</v>
       </c>
@@ -7091,7 +7092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>443</v>
       </c>
@@ -7099,7 +7100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>444</v>
       </c>
@@ -7107,7 +7108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>445</v>
       </c>
@@ -7115,7 +7116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>446</v>
       </c>
@@ -7123,7 +7124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>447</v>
       </c>
@@ -7131,7 +7132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>448</v>
       </c>
@@ -7139,7 +7140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>449</v>
       </c>
@@ -7147,7 +7148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>450</v>
       </c>
@@ -7155,7 +7156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>451</v>
       </c>
@@ -7163,7 +7164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>452</v>
       </c>
@@ -7171,7 +7172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>453</v>
       </c>
@@ -7179,7 +7180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>454</v>
       </c>
@@ -7187,7 +7188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>455</v>
       </c>
@@ -7195,7 +7196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>456</v>
       </c>
@@ -7203,7 +7204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>457</v>
       </c>
@@ -7211,7 +7212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>458</v>
       </c>
@@ -7219,7 +7220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>459</v>
       </c>
@@ -7227,7 +7228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>460</v>
       </c>
@@ -7235,7 +7236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>461</v>
       </c>
@@ -7243,7 +7244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>462</v>
       </c>
@@ -7251,7 +7252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>463</v>
       </c>
@@ -7259,7 +7260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>464</v>
       </c>
@@ -7267,7 +7268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>465</v>
       </c>
@@ -7275,7 +7276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>466</v>
       </c>
@@ -7283,7 +7284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>467</v>
       </c>
@@ -7291,7 +7292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>468</v>
       </c>
@@ -7299,7 +7300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>469</v>
       </c>
@@ -7307,7 +7308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>470</v>
       </c>
@@ -7315,7 +7316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>471</v>
       </c>
@@ -7323,7 +7324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>472</v>
       </c>
@@ -7331,7 +7332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>473</v>
       </c>
@@ -7339,7 +7340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>474</v>
       </c>
@@ -7347,7 +7348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>475</v>
       </c>
@@ -7355,7 +7356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>476</v>
       </c>
@@ -7363,7 +7364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>477</v>
       </c>
@@ -7371,7 +7372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>478</v>
       </c>
@@ -7379,7 +7380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>479</v>
       </c>
@@ -7387,7 +7388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>480</v>
       </c>
@@ -7395,7 +7396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>481</v>
       </c>
@@ -7403,7 +7404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>482</v>
       </c>
@@ -7411,7 +7412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>483</v>
       </c>
@@ -7419,7 +7420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>484</v>
       </c>
@@ -7427,7 +7428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>485</v>
       </c>
@@ -7435,7 +7436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>486</v>
       </c>
@@ -7443,7 +7444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>487</v>
       </c>
@@ -7451,7 +7452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>488</v>
       </c>
@@ -7459,7 +7460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>489</v>
       </c>
@@ -7467,7 +7468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>490</v>
       </c>
@@ -7475,7 +7476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>491</v>
       </c>
@@ -7483,7 +7484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>492</v>
       </c>
@@ -7491,7 +7492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>493</v>
       </c>
@@ -7499,7 +7500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>494</v>
       </c>
@@ -7507,7 +7508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>495</v>
       </c>
@@ -7515,7 +7516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>496</v>
       </c>
@@ -7523,7 +7524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>497</v>
       </c>
@@ -7531,7 +7532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>498</v>
       </c>
@@ -7539,7 +7540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>499</v>
       </c>
@@ -7547,7 +7548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>500</v>
       </c>
@@ -7555,7 +7556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>501</v>
       </c>
@@ -7563,7 +7564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>502</v>
       </c>
@@ -7571,7 +7572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>503</v>
       </c>
@@ -7579,7 +7580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>504</v>
       </c>
@@ -7587,7 +7588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>505</v>
       </c>
@@ -7595,7 +7596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>506</v>
       </c>
@@ -7603,7 +7604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>507</v>
       </c>
@@ -7611,7 +7612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>508</v>
       </c>
@@ -7619,7 +7620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>509</v>
       </c>
@@ -7627,7 +7628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>510</v>
       </c>
@@ -7635,7 +7636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>511</v>
       </c>
@@ -7643,7 +7644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>512</v>
       </c>
@@ -7651,7 +7652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>513</v>
       </c>
@@ -7659,7 +7660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>514</v>
       </c>
@@ -7667,7 +7668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>515</v>
       </c>
@@ -7675,7 +7676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>516</v>
       </c>
@@ -7691,7 +7692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>518</v>
       </c>
@@ -7699,7 +7700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>519</v>
       </c>
@@ -7707,7 +7708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>520</v>
       </c>
@@ -7715,7 +7716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>521</v>
       </c>
@@ -7723,7 +7724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>522</v>
       </c>
@@ -7731,7 +7732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>523</v>
       </c>
@@ -7739,7 +7740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>524</v>
       </c>
@@ -7747,7 +7748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>525</v>
       </c>
@@ -7755,7 +7756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>526</v>
       </c>
@@ -7763,7 +7764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>527</v>
       </c>
@@ -7771,7 +7772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>528</v>
       </c>
@@ -7779,7 +7780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>529</v>
       </c>
@@ -7787,7 +7788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>530</v>
       </c>
@@ -7795,7 +7796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>531</v>
       </c>
@@ -7803,7 +7804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>532</v>
       </c>
@@ -7811,7 +7812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>533</v>
       </c>
@@ -7819,7 +7820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>534</v>
       </c>
@@ -7827,7 +7828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>535</v>
       </c>
@@ -7835,7 +7836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>536</v>
       </c>
@@ -7843,7 +7844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>537</v>
       </c>
@@ -7851,7 +7852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>538</v>
       </c>
@@ -7859,7 +7860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>539</v>
       </c>
@@ -7867,7 +7868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>540</v>
       </c>
@@ -7875,7 +7876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>541</v>
       </c>
@@ -7883,7 +7884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>542</v>
       </c>
@@ -7891,7 +7892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>543</v>
       </c>
@@ -7899,7 +7900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>544</v>
       </c>
@@ -7907,7 +7908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>545</v>
       </c>
@@ -7915,7 +7916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>546</v>
       </c>
@@ -7923,7 +7924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>547</v>
       </c>
@@ -7931,7 +7932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>548</v>
       </c>
@@ -7939,7 +7940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>549</v>
       </c>
@@ -7947,7 +7948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>550</v>
       </c>
@@ -7955,7 +7956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>551</v>
       </c>
@@ -7963,7 +7964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>552</v>
       </c>
@@ -7971,7 +7972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>553</v>
       </c>
@@ -7979,7 +7980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>554</v>
       </c>
@@ -7987,7 +7988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>555</v>
       </c>
@@ -7995,7 +7996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>556</v>
       </c>
@@ -8003,7 +8004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>557</v>
       </c>
@@ -8011,7 +8012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>558</v>
       </c>
@@ -8019,7 +8020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>559</v>
       </c>
@@ -8027,7 +8028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>560</v>
       </c>
@@ -8035,7 +8036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>561</v>
       </c>
@@ -8043,7 +8044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>562</v>
       </c>
@@ -8051,7 +8052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>563</v>
       </c>
@@ -8083,7 +8084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>567</v>
       </c>
@@ -8091,7 +8092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>568</v>
       </c>
@@ -8099,7 +8100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>569</v>
       </c>
@@ -8107,7 +8108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>570</v>
       </c>
@@ -8115,7 +8116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>571</v>
       </c>
@@ -8123,7 +8124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>572</v>
       </c>
@@ -8131,7 +8132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>573</v>
       </c>
@@ -8139,7 +8140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>574</v>
       </c>
@@ -8147,7 +8148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>575</v>
       </c>
@@ -8155,7 +8156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>576</v>
       </c>
@@ -8163,7 +8164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>577</v>
       </c>
@@ -8171,7 +8172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>578</v>
       </c>
@@ -8179,7 +8180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>579</v>
       </c>
@@ -8187,7 +8188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>580</v>
       </c>
@@ -8195,7 +8196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>581</v>
       </c>
@@ -8203,7 +8204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>582</v>
       </c>
@@ -8211,7 +8212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>583</v>
       </c>
@@ -8219,7 +8220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>584</v>
       </c>
@@ -8227,7 +8228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>585</v>
       </c>
@@ -8235,7 +8236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>586</v>
       </c>
@@ -8243,7 +8244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>587</v>
       </c>
@@ -8251,7 +8252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>588</v>
       </c>
@@ -8259,7 +8260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>589</v>
       </c>
@@ -8267,7 +8268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>590</v>
       </c>
@@ -8275,7 +8276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>591</v>
       </c>
@@ -8283,7 +8284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>592</v>
       </c>
@@ -8291,7 +8292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>593</v>
       </c>
@@ -8299,7 +8300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>594</v>
       </c>
@@ -8307,7 +8308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>595</v>
       </c>
@@ -8315,7 +8316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>596</v>
       </c>
@@ -8323,7 +8324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>597</v>
       </c>
@@ -8331,7 +8332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>598</v>
       </c>
@@ -8339,7 +8340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>599</v>
       </c>
@@ -8347,7 +8348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>600</v>
       </c>
@@ -8355,7 +8356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>601</v>
       </c>
@@ -8363,7 +8364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>602</v>
       </c>
@@ -8371,7 +8372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>603</v>
       </c>
@@ -8379,7 +8380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>604</v>
       </c>
@@ -8387,7 +8388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>605</v>
       </c>
@@ -8395,7 +8396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>606</v>
       </c>
@@ -8411,7 +8412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>608</v>
       </c>
@@ -8419,7 +8420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>609</v>
       </c>
@@ -8427,7 +8428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>610</v>
       </c>
@@ -8435,7 +8436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>611</v>
       </c>
@@ -8443,7 +8444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>612</v>
       </c>
@@ -8451,7 +8452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>613</v>
       </c>
@@ -8475,7 +8476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>616</v>
       </c>
@@ -8483,7 +8484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>617</v>
       </c>
@@ -8491,7 +8492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>618</v>
       </c>
@@ -8499,7 +8500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>619</v>
       </c>
@@ -8507,7 +8508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>620</v>
       </c>
@@ -8515,7 +8516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>621</v>
       </c>
@@ -8523,7 +8524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>622</v>
       </c>
@@ -8531,7 +8532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>623</v>
       </c>
@@ -8539,7 +8540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>624</v>
       </c>
@@ -8547,7 +8548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>625</v>
       </c>
@@ -8555,7 +8556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>626</v>
       </c>
@@ -8563,7 +8564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>627</v>
       </c>
@@ -8571,7 +8572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>628</v>
       </c>
@@ -8651,7 +8652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>638</v>
       </c>
@@ -8659,7 +8660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>639</v>
       </c>
@@ -8667,7 +8668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>640</v>
       </c>
@@ -8675,7 +8676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>641</v>
       </c>
@@ -8683,7 +8684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>642</v>
       </c>
@@ -8691,7 +8692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>643</v>
       </c>
@@ -8699,7 +8700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>644</v>
       </c>
@@ -8707,7 +8708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>645</v>
       </c>
@@ -8715,7 +8716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>646</v>
       </c>
@@ -8723,7 +8724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>647</v>
       </c>
@@ -8731,7 +8732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>648</v>
       </c>
@@ -8739,7 +8740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>649</v>
       </c>
@@ -8747,7 +8748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>650</v>
       </c>
@@ -8755,7 +8756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>651</v>
       </c>
@@ -8763,7 +8764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>652</v>
       </c>
@@ -8771,7 +8772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>653</v>
       </c>
@@ -8779,7 +8780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>654</v>
       </c>
@@ -8787,7 +8788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>655</v>
       </c>
@@ -8795,7 +8796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>656</v>
       </c>
@@ -8803,7 +8804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>657</v>
       </c>
@@ -8811,7 +8812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>658</v>
       </c>
@@ -8827,7 +8828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>660</v>
       </c>
@@ -8835,7 +8836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>661</v>
       </c>
@@ -8843,7 +8844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>662</v>
       </c>
@@ -8851,7 +8852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>663</v>
       </c>
@@ -8859,7 +8860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>664</v>
       </c>
@@ -8899,7 +8900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>669</v>
       </c>
@@ -8907,7 +8908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>670</v>
       </c>
@@ -8915,7 +8916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>671</v>
       </c>
@@ -8923,7 +8924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>672</v>
       </c>
@@ -8931,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>673</v>
       </c>
@@ -8939,7 +8940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>674</v>
       </c>
@@ -8947,7 +8948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>675</v>
       </c>
@@ -8955,7 +8956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>676</v>
       </c>
@@ -8963,7 +8964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>677</v>
       </c>
@@ -8971,7 +8972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>678</v>
       </c>
@@ -8979,7 +8980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>679</v>
       </c>
@@ -8987,7 +8988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>680</v>
       </c>
@@ -8995,7 +8996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>681</v>
       </c>
@@ -9003,7 +9004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>682</v>
       </c>
@@ -9011,7 +9012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>683</v>
       </c>
@@ -9019,7 +9020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>684</v>
       </c>
@@ -9027,7 +9028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>685</v>
       </c>
@@ -9211,7 +9212,7 @@
         <v>296.79599999999999</v>
       </c>
     </row>
-    <row r="701" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>699</v>
       </c>
@@ -9219,7 +9220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>700</v>
       </c>
@@ -9227,7 +9228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>701</v>
       </c>
@@ -9235,7 +9236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="704" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>702</v>
       </c>
@@ -9243,7 +9244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>703</v>
       </c>
@@ -9251,7 +9252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>704</v>
       </c>
@@ -9259,7 +9260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="707" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>705</v>
       </c>
@@ -9267,7 +9268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>706</v>
       </c>
@@ -9275,7 +9276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>707</v>
       </c>
@@ -9283,7 +9284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="710" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>708</v>
       </c>
@@ -9291,7 +9292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>709</v>
       </c>
@@ -9299,7 +9300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="712" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>710</v>
       </c>
@@ -9307,7 +9308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>711</v>
       </c>
@@ -9315,7 +9316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="714" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>712</v>
       </c>
@@ -9323,7 +9324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>713</v>
       </c>
@@ -9331,7 +9332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="716" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>714</v>
       </c>
@@ -9339,7 +9340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>715</v>
       </c>
@@ -9347,7 +9348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>716</v>
       </c>
@@ -9355,7 +9356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>717</v>
       </c>
@@ -9363,7 +9364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="720" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>718</v>
       </c>
@@ -9371,7 +9372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="721" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>719</v>
       </c>
@@ -9379,7 +9380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="722" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>720</v>
       </c>
@@ -9387,7 +9388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>721</v>
       </c>
@@ -9395,7 +9396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="724" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>722</v>
       </c>
@@ -9403,7 +9404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="725" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>723</v>
       </c>
@@ -9411,7 +9412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="726" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>724</v>
       </c>
@@ -9419,7 +9420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="727" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>725</v>
       </c>
@@ -9427,7 +9428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="728" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>726</v>
       </c>
@@ -9435,7 +9436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="729" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>727</v>
       </c>
@@ -9443,7 +9444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="730" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>728</v>
       </c>
@@ -9451,7 +9452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="731" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>729</v>
       </c>
@@ -9459,7 +9460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="732" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>730</v>
       </c>
@@ -9467,7 +9468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="733" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>731</v>
       </c>
@@ -9475,7 +9476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="734" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>732</v>
       </c>
@@ -9483,7 +9484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="735" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>733</v>
       </c>
@@ -9491,7 +9492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="736" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>734</v>
       </c>
@@ -9499,7 +9500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>735</v>
       </c>
@@ -9507,7 +9508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="738" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>736</v>
       </c>
@@ -9515,7 +9516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="739" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>737</v>
       </c>
@@ -9523,7 +9524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="740" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>738</v>
       </c>
@@ -9531,7 +9532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="741" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>739</v>
       </c>
@@ -9539,7 +9540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="742" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>740</v>
       </c>
@@ -9547,7 +9548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="743" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>741</v>
       </c>
@@ -9555,7 +9556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="744" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>742</v>
       </c>
@@ -9563,7 +9564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="745" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>743</v>
       </c>
@@ -9571,7 +9572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="746" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>744</v>
       </c>
@@ -9579,7 +9580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="747" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>745</v>
       </c>
@@ -9587,7 +9588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="748" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>746</v>
       </c>
@@ -9595,7 +9596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="749" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>747</v>
       </c>
@@ -9603,7 +9604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="750" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>748</v>
       </c>
@@ -9611,7 +9612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="751" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>749</v>
       </c>
@@ -9619,7 +9620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="752" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>750</v>
       </c>
@@ -9627,7 +9628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="753" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>751</v>
       </c>
@@ -9635,7 +9636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>752</v>
       </c>
@@ -9643,7 +9644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="755" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>753</v>
       </c>
@@ -9651,7 +9652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>754</v>
       </c>
@@ -9659,7 +9660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="757" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>755</v>
       </c>
@@ -9667,7 +9668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>756</v>
       </c>
@@ -9675,7 +9676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="759" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>757</v>
       </c>
@@ -9683,7 +9684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="760" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>758</v>
       </c>
@@ -9691,7 +9692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="761" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>759</v>
       </c>
@@ -9699,7 +9700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="762" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>760</v>
       </c>
@@ -9707,7 +9708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="763" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>761</v>
       </c>
@@ -9715,7 +9716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="764" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>762</v>
       </c>
@@ -9731,7 +9732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="766" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>764</v>
       </c>
@@ -9739,7 +9740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="767" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>765</v>
       </c>
@@ -9747,7 +9748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="768" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>766</v>
       </c>
@@ -9755,7 +9756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="769" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>767</v>
       </c>
@@ -9763,7 +9764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="770" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>768</v>
       </c>
@@ -9771,7 +9772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="771" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>769</v>
       </c>
@@ -9779,7 +9780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="772" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>770</v>
       </c>
@@ -9787,7 +9788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="773" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>771</v>
       </c>
@@ -9795,7 +9796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="774" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>772</v>
       </c>
@@ -9803,7 +9804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="775" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>773</v>
       </c>
@@ -9811,7 +9812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="776" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>774</v>
       </c>
@@ -9819,7 +9820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="777" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>775</v>
       </c>
@@ -9827,7 +9828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="778" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>776</v>
       </c>
@@ -9835,7 +9836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="779" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>777</v>
       </c>
@@ -9851,7 +9852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="781" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>779</v>
       </c>
@@ -9859,7 +9860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="782" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>780</v>
       </c>
@@ -9867,7 +9868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="783" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>781</v>
       </c>
@@ -9875,7 +9876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="784" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>782</v>
       </c>
@@ -9883,7 +9884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="785" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>783</v>
       </c>
@@ -9891,7 +9892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="786" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>784</v>
       </c>
@@ -9899,7 +9900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="787" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>785</v>
       </c>
@@ -9907,7 +9908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="788" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>786</v>
       </c>
@@ -9915,7 +9916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="789" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>787</v>
       </c>
@@ -9923,7 +9924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="790" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>788</v>
       </c>
@@ -9931,7 +9932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="791" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>789</v>
       </c>
@@ -9939,7 +9940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="792" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>790</v>
       </c>
@@ -9947,7 +9948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="793" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>791</v>
       </c>
@@ -9955,7 +9956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="794" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>792</v>
       </c>
@@ -9963,7 +9964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="795" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>793</v>
       </c>
@@ -9971,7 +9972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="796" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>794</v>
       </c>
@@ -9979,7 +9980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="797" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>795</v>
       </c>
@@ -9987,7 +9988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="798" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>796</v>
       </c>
@@ -9995,7 +9996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="799" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>797</v>
       </c>
@@ -10003,7 +10004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="800" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>798</v>
       </c>
@@ -10011,7 +10012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="801" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>799</v>
       </c>
@@ -10019,7 +10020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="802" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>800</v>
       </c>
@@ -10027,7 +10028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="803" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>801</v>
       </c>
@@ -10035,7 +10036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="804" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>802</v>
       </c>
@@ -10043,7 +10044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="805" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>803</v>
       </c>
@@ -10051,7 +10052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="806" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>804</v>
       </c>
@@ -10059,7 +10060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="807" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>805</v>
       </c>
@@ -10067,7 +10068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="808" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>806</v>
       </c>
@@ -10075,7 +10076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="809" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>807</v>
       </c>
@@ -10083,7 +10084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="810" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>808</v>
       </c>
@@ -10091,7 +10092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="811" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>809</v>
       </c>
@@ -10099,7 +10100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="812" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>810</v>
       </c>
@@ -10107,7 +10108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="813" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>811</v>
       </c>
@@ -10115,7 +10116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="814" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>812</v>
       </c>
@@ -10123,7 +10124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="815" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>813</v>
       </c>
@@ -10131,7 +10132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="816" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>814</v>
       </c>
@@ -10139,7 +10140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="817" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>815</v>
       </c>
@@ -10147,7 +10148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="818" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>816</v>
       </c>
@@ -10155,7 +10156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="819" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>817</v>
       </c>
@@ -10163,7 +10164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="820" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>818</v>
       </c>
@@ -10171,7 +10172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="821" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>819</v>
       </c>
@@ -10179,7 +10180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="822" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>820</v>
       </c>
@@ -10187,7 +10188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="823" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>821</v>
       </c>
@@ -10195,7 +10196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="824" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>822</v>
       </c>
@@ -10203,7 +10204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="825" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>823</v>
       </c>
@@ -10219,7 +10220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="827" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>825</v>
       </c>
@@ -10227,7 +10228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="828" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>826</v>
       </c>
@@ -10235,7 +10236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="829" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>827</v>
       </c>
@@ -10243,7 +10244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="830" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>828</v>
       </c>
@@ -10251,7 +10252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="831" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>829</v>
       </c>
@@ -10259,7 +10260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="832" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>830</v>
       </c>
@@ -10267,7 +10268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="833" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
         <v>831</v>
       </c>
@@ -10275,7 +10276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="834" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
         <v>832</v>
       </c>
@@ -10283,7 +10284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="835" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
         <v>833</v>
       </c>
@@ -10299,7 +10300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="837" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
         <v>835</v>
       </c>
@@ -10307,7 +10308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="838" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
         <v>836</v>
       </c>
@@ -10315,7 +10316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="839" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
         <v>837</v>
       </c>
@@ -10323,7 +10324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="840" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
         <v>838</v>
       </c>
@@ -10331,7 +10332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="841" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
         <v>839</v>
       </c>
@@ -10339,7 +10340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="842" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
         <v>840</v>
       </c>
@@ -10347,7 +10348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="843" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
         <v>841</v>
       </c>
@@ -10355,7 +10356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="844" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
         <v>842</v>
       </c>
@@ -10363,7 +10364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="845" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
         <v>843</v>
       </c>
@@ -10371,7 +10372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="846" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
         <v>844</v>
       </c>
@@ -10379,7 +10380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="847" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
         <v>845</v>
       </c>
@@ -10387,7 +10388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="848" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
         <v>846</v>
       </c>
@@ -10395,7 +10396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="849" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
         <v>847</v>
       </c>
@@ -10403,7 +10404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="850" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
         <v>848</v>
       </c>
@@ -10411,7 +10412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="851" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A851" t="s">
         <v>849</v>
       </c>
@@ -10419,7 +10420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="852" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A852" t="s">
         <v>850</v>
       </c>
@@ -10427,7 +10428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="853" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="853" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A853" t="s">
         <v>851</v>
       </c>
@@ -10435,7 +10436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="854" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
         <v>852</v>
       </c>
@@ -10443,7 +10444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="855" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A855" t="s">
         <v>853</v>
       </c>
@@ -10451,7 +10452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="856" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
         <v>854</v>
       </c>
@@ -10459,7 +10460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="857" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
         <v>855</v>
       </c>
@@ -10475,7 +10476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="859" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A859" t="s">
         <v>857</v>
       </c>
@@ -10483,7 +10484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="860" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
         <v>858</v>
       </c>
@@ -10491,7 +10492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="861" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
         <v>859</v>
       </c>
@@ -10499,7 +10500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="862" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
         <v>860</v>
       </c>
@@ -10507,7 +10508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="863" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="863" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A863" t="s">
         <v>861</v>
       </c>
@@ -10515,7 +10516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="864" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="864" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A864" t="s">
         <v>862</v>
       </c>
@@ -10523,7 +10524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="865" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="865" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A865" t="s">
         <v>863</v>
       </c>
@@ -10531,7 +10532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="866" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="866" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A866" t="s">
         <v>864</v>
       </c>
@@ -10539,7 +10540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="867" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="867" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
         <v>865</v>
       </c>
@@ -10547,7 +10548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="868" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="868" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A868" t="s">
         <v>866</v>
       </c>
@@ -10555,7 +10556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="869" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="869" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A869" t="s">
         <v>867</v>
       </c>
@@ -10563,7 +10564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="870" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="870" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A870" t="s">
         <v>868</v>
       </c>
@@ -10571,7 +10572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="871" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="871" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A871" t="s">
         <v>869</v>
       </c>
@@ -10579,7 +10580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="872" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="872" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A872" t="s">
         <v>870</v>
       </c>
@@ -10587,7 +10588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="873" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="873" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A873" t="s">
         <v>871</v>
       </c>
@@ -10595,7 +10596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="874" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="874" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A874" t="s">
         <v>872</v>
       </c>
@@ -10603,7 +10604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="875" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="875" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A875" t="s">
         <v>873</v>
       </c>
@@ -10611,7 +10612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="876" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="876" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A876" t="s">
         <v>874</v>
       </c>
@@ -10619,7 +10620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="877" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="877" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A877" t="s">
         <v>875</v>
       </c>
@@ -10627,7 +10628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="878" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="878" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A878" t="s">
         <v>876</v>
       </c>
@@ -10635,7 +10636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="879" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="879" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A879" t="s">
         <v>877</v>
       </c>
@@ -10643,7 +10644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="880" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="880" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A880" t="s">
         <v>878</v>
       </c>
@@ -10651,7 +10652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="881" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="881" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A881" t="s">
         <v>879</v>
       </c>
@@ -10659,7 +10660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="882" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="882" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A882" t="s">
         <v>880</v>
       </c>
@@ -10667,7 +10668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="883" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="883" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A883" t="s">
         <v>881</v>
       </c>
@@ -10675,7 +10676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="884" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="884" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A884" t="s">
         <v>882</v>
       </c>
@@ -10683,7 +10684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="885" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="885" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A885" t="s">
         <v>883</v>
       </c>
@@ -10691,7 +10692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="886" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="886" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A886" t="s">
         <v>884</v>
       </c>
@@ -10699,7 +10700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="887" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="887" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A887" t="s">
         <v>885</v>
       </c>
@@ -10707,7 +10708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="888" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="888" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A888" t="s">
         <v>886</v>
       </c>
@@ -10715,7 +10716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="889" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="889" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A889" t="s">
         <v>887</v>
       </c>
@@ -10723,7 +10724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="890" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="890" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A890" t="s">
         <v>888</v>
       </c>
@@ -10731,7 +10732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="891" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="891" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A891" t="s">
         <v>889</v>
       </c>
@@ -10739,7 +10740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="892" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="892" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A892" t="s">
         <v>890</v>
       </c>
@@ -10755,7 +10756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="894" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="894" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A894" t="s">
         <v>892</v>
       </c>
@@ -10763,7 +10764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="895" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="895" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A895" t="s">
         <v>893</v>
       </c>
@@ -10771,7 +10772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="896" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="896" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A896" t="s">
         <v>894</v>
       </c>
@@ -10779,7 +10780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="897" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="897" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A897" t="s">
         <v>895</v>
       </c>
@@ -10787,7 +10788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="898" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="898" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A898" t="s">
         <v>896</v>
       </c>
@@ -10795,7 +10796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="899" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="899" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A899" t="s">
         <v>897</v>
       </c>
@@ -10803,7 +10804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="900" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="900" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A900" t="s">
         <v>898</v>
       </c>
@@ -10811,7 +10812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="901" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="901" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A901" t="s">
         <v>899</v>
       </c>
@@ -10819,7 +10820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="902" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="902" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A902" t="s">
         <v>900</v>
       </c>
@@ -10827,7 +10828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="903" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="903" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A903" t="s">
         <v>901</v>
       </c>
@@ -10835,7 +10836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="904" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="904" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A904" t="s">
         <v>902</v>
       </c>
@@ -10843,7 +10844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="905" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="905" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A905" t="s">
         <v>903</v>
       </c>
@@ -10851,7 +10852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="906" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="906" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A906" t="s">
         <v>904</v>
       </c>
@@ -10859,7 +10860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="907" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="907" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A907" t="s">
         <v>905</v>
       </c>
@@ -10867,7 +10868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="908" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="908" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A908" t="s">
         <v>906</v>
       </c>
@@ -10875,7 +10876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="909" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A909" t="s">
         <v>907</v>
       </c>
@@ -10883,7 +10884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="910" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="910" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A910" t="s">
         <v>908</v>
       </c>
@@ -10891,7 +10892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="911" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="911" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A911" t="s">
         <v>909</v>
       </c>
@@ -10899,7 +10900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="912" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="912" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A912" t="s">
         <v>910</v>
       </c>
@@ -10907,7 +10908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="913" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="913" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A913" t="s">
         <v>911</v>
       </c>
@@ -10915,7 +10916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="914" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="914" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A914" t="s">
         <v>912</v>
       </c>
@@ -10923,7 +10924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="915" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="915" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A915" t="s">
         <v>913</v>
       </c>
@@ -10931,7 +10932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="916" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="916" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A916" t="s">
         <v>914</v>
       </c>
@@ -10939,7 +10940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="917" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="917" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A917" t="s">
         <v>915</v>
       </c>
@@ -10947,7 +10948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="918" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="918" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A918" t="s">
         <v>916</v>
       </c>
@@ -10955,7 +10956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="919" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="919" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A919" t="s">
         <v>917</v>
       </c>
@@ -10963,7 +10964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="920" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="920" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A920" t="s">
         <v>918</v>
       </c>
@@ -10971,7 +10972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="921" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="921" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A921" t="s">
         <v>919</v>
       </c>
@@ -10979,7 +10980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="922" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="922" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A922" t="s">
         <v>920</v>
       </c>
@@ -10987,7 +10988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="923" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="923" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A923" t="s">
         <v>921</v>
       </c>
@@ -10995,7 +10996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="924" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="924" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A924" t="s">
         <v>922</v>
       </c>
@@ -11003,7 +11004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="925" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="925" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A925" t="s">
         <v>923</v>
       </c>
@@ -11011,7 +11012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="926" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="926" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A926" t="s">
         <v>924</v>
       </c>
@@ -11019,7 +11020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="927" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="927" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A927" t="s">
         <v>925</v>
       </c>
@@ -11027,7 +11028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="928" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="928" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A928" t="s">
         <v>926</v>
       </c>
@@ -11035,7 +11036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="929" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="929" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A929" t="s">
         <v>927</v>
       </c>
@@ -11043,7 +11044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="930" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="930" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A930" t="s">
         <v>928</v>
       </c>
@@ -11051,7 +11052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="931" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="931" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A931" t="s">
         <v>929</v>
       </c>
@@ -11059,7 +11060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="932" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="932" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A932" t="s">
         <v>930</v>
       </c>
@@ -11067,7 +11068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="933" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="933" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A933" t="s">
         <v>931</v>
       </c>
@@ -11075,7 +11076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="934" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="934" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
         <v>932</v>
       </c>
@@ -11083,7 +11084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="935" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="935" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A935" t="s">
         <v>933</v>
       </c>
@@ -11091,7 +11092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="936" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="936" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A936" t="s">
         <v>934</v>
       </c>
@@ -11099,7 +11100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="937" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="937" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A937" t="s">
         <v>935</v>
       </c>
@@ -11115,7 +11116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="939" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="939" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A939" t="s">
         <v>937</v>
       </c>
@@ -11123,7 +11124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="940" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="940" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A940" t="s">
         <v>938</v>
       </c>
@@ -11131,7 +11132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="941" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="941" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A941" t="s">
         <v>939</v>
       </c>
@@ -11139,7 +11140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="942" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="942" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A942" t="s">
         <v>940</v>
       </c>
@@ -11147,7 +11148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="943" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="943" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A943" t="s">
         <v>941</v>
       </c>
@@ -11203,7 +11204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="950" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="950" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
         <v>948</v>
       </c>
@@ -11219,7 +11220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="952" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="952" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
         <v>950</v>
       </c>
@@ -11227,7 +11228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="953" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="953" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
         <v>951</v>
       </c>
@@ -11235,7 +11236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="954" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="954" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
         <v>952</v>
       </c>
@@ -11243,7 +11244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="955" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="955" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
         <v>953</v>
       </c>
@@ -11251,7 +11252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="956" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="956" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
         <v>954</v>
       </c>
@@ -11259,7 +11260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="957" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="957" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
         <v>955</v>
       </c>
@@ -11267,7 +11268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="958" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="958" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A958" t="s">
         <v>956</v>
       </c>
@@ -11275,7 +11276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="959" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="959" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A959" t="s">
         <v>957</v>
       </c>
@@ -11283,7 +11284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="960" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="960" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A960" t="s">
         <v>958</v>
       </c>
@@ -11291,7 +11292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="961" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="961" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A961" t="s">
         <v>959</v>
       </c>
@@ -11299,7 +11300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="962" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="962" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A962" t="s">
         <v>960</v>
       </c>
@@ -11307,7 +11308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="963" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="963" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A963" t="s">
         <v>961</v>
       </c>
@@ -11315,7 +11316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="964" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="964" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A964" t="s">
         <v>962</v>
       </c>
@@ -11323,7 +11324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="965" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="965" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A965" t="s">
         <v>963</v>
       </c>
@@ -11331,7 +11332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="966" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="966" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A966" t="s">
         <v>964</v>
       </c>
@@ -11347,7 +11348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="968" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="968" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A968" t="s">
         <v>966</v>
       </c>
@@ -11355,7 +11356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="969" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="969" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A969" t="s">
         <v>967</v>
       </c>
@@ -11363,7 +11364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="970" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="970" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A970" t="s">
         <v>968</v>
       </c>
@@ -11371,7 +11372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="971" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="971" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A971" t="s">
         <v>969</v>
       </c>
@@ -11379,7 +11380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="972" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="972" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A972" t="s">
         <v>970</v>
       </c>
@@ -11387,7 +11388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="973" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="973" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A973" t="s">
         <v>971</v>
       </c>
@@ -11395,7 +11396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="974" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="974" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A974" t="s">
         <v>972</v>
       </c>
@@ -11403,7 +11404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="975" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="975" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A975" t="s">
         <v>973</v>
       </c>
@@ -11411,7 +11412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="976" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="976" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A976" t="s">
         <v>974</v>
       </c>
@@ -11419,7 +11420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="977" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="977" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A977" t="s">
         <v>975</v>
       </c>
@@ -11427,7 +11428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="978" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="978" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A978" t="s">
         <v>976</v>
       </c>
@@ -11724,7 +11725,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B992" xr:uid="{DCA4F88A-3EEB-45AF-91DF-E65A060D6362}"/>
+  <autoFilter ref="B1:B1014" xr:uid="{DCA4F88A-3EEB-45AF-91DF-E65A060D6362}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/dataAcquisition/Motec_MP/channels/channels.xlsx
+++ b/dataAcquisition/Motec_MP/channels/channels.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SimEnv\dataAcquisition\Motec_MP\channels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D1C7E4C-9398-4992-A9BD-303D0A6570EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179BC2AD-196E-44B9-8E86-AB4AB82ED90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="420" windowWidth="20136" windowHeight="13680" xr2:uid="{6EEC8272-D558-43BF-A2F2-0B52778D7332}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{6EEC8272-D558-43BF-A2F2-0B52778D7332}"/>
   </bookViews>
   <sheets>
     <sheet name="channels" sheetId="2" r:id="rId1"/>
     <sheet name="gatedChannels" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="5" r:id="rId3"/>
+    <sheet name="matlabCreatedGates" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">channels!$B$1:$B$1014</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="1029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="1069">
   <si>
     <t xml:space="preserve">Beacon                </t>
   </si>
@@ -3128,6 +3128,126 @@
   </si>
   <si>
     <t>Fuel_Density_Corr_Linear</t>
+  </si>
+  <si>
+    <t>brakingGateVCH .* CLa_SCz_VCH</t>
+  </si>
+  <si>
+    <t>CLa_SCz_Braking_VCH</t>
+  </si>
+  <si>
+    <t>entryGateVCH .* CLa_SCz_VCH</t>
+  </si>
+  <si>
+    <t>CLa_SCz_Entry_VCH</t>
+  </si>
+  <si>
+    <t>midCrnGateVCH .* CLa_SCz_VCH</t>
+  </si>
+  <si>
+    <t>CLa_SCz_MidCrn_VCH</t>
+  </si>
+  <si>
+    <t>exitGateVCH .* CLa_SCz_VCH</t>
+  </si>
+  <si>
+    <t>CLa_SCz_Exit_VCH</t>
+  </si>
+  <si>
+    <t>Parity_Speed .* Ground_Speed</t>
+  </si>
+  <si>
+    <t>Parity _Speed</t>
+  </si>
+  <si>
+    <t>Ground_Speed_low_VCH.*CDa_SCx_VCH</t>
+  </si>
+  <si>
+    <t>Ground_Speed_Mid_VCH.*CDa_SCx_VCH</t>
+  </si>
+  <si>
+    <t>Ground_Speed_High_VCH.*CDa_SCx_VCH</t>
+  </si>
+  <si>
+    <t>ParityMaskVCH.*CDa_SCx_VCH</t>
+  </si>
+  <si>
+    <t>Low_Speed_Cx</t>
+  </si>
+  <si>
+    <t>Mid_Speed_Cx</t>
+  </si>
+  <si>
+    <t>High_Speed_SCx</t>
+  </si>
+  <si>
+    <t>Parity _Speed_Cx</t>
+  </si>
+  <si>
+    <t>Parity_Speed</t>
+  </si>
+  <si>
+    <t>AB_FRT_VCH.*brakingGateVCH</t>
+  </si>
+  <si>
+    <t>AB_FRT_VCH.*entryGateVCH</t>
+  </si>
+  <si>
+    <t>AB_FRT_VCH.*midCrnGateVCH</t>
+  </si>
+  <si>
+    <t>AB_FRT_VCH.*exitGateVCH</t>
+  </si>
+  <si>
+    <t>EFF_VCH.*brakingGateVCH</t>
+  </si>
+  <si>
+    <t>EFF_VCH.*entryGateVCH</t>
+  </si>
+  <si>
+    <t>EFF_VCH.*midCrnGateVCH</t>
+  </si>
+  <si>
+    <t>EFF_VCH.*exitGateVCH</t>
+  </si>
+  <si>
+    <t>CSa_Scy_VCH.*entryGateVCH</t>
+  </si>
+  <si>
+    <t>CSa_Scy_VCH.*midCrnGateVCH</t>
+  </si>
+  <si>
+    <t>AB_Braking</t>
+  </si>
+  <si>
+    <t>AB_Entry</t>
+  </si>
+  <si>
+    <t>AB_Exit</t>
+  </si>
+  <si>
+    <t>EFF_MidCrn</t>
+  </si>
+  <si>
+    <t>SideForce_Entry</t>
+  </si>
+  <si>
+    <t>SideForce_Midcrn</t>
+  </si>
+  <si>
+    <t>AB_Midcrn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>EFF_Braking</t>
+  </si>
+  <si>
+    <t>EFF_Entryy</t>
+  </si>
+  <si>
+    <t>EFF_Exit</t>
   </si>
 </sst>
 </file>
@@ -3500,7 +3620,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA4F88A-3EEB-45AF-91DF-E65A060D6362}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E1014"/>
+  <dimension ref="A1:E1024"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.44140625" bestFit="1" customWidth="1"/>
@@ -11722,6 +11842,43 @@
       </c>
       <c r="B1014">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1015" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B1015">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1016" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B1016">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1017" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B1017">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1018" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B1018">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1024" t="s">
+        <v>1065</v>
       </c>
     </row>
   </sheetData>
@@ -11739,11 +11896,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5608434B-CD06-48FB-B215-551DA4295CD4}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -11824,6 +11990,158 @@
       </c>
       <c r="B10" t="s">
         <v>1023</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1063</v>
       </c>
     </row>
   </sheetData>
@@ -11834,7 +12152,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DBC5ABB-F849-47F0-90C0-9E706E77A496}">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -11900,6 +12218,11 @@
         <v>990</v>
       </c>
     </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1047</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
